--- a/samsung/dist/20261025_三星電子模型_v0.3.1.xlsx
+++ b/samsung/dist/20261025_三星電子模型_v0.3.1.xlsx
@@ -83,17 +83,41 @@
     <definedName function="false" hidden="false" name="cqB_8" vbProcedure="false">In!$E$100</definedName>
     <definedName function="false" hidden="false" name="cqB_9" vbProcedure="false">In!$E$101</definedName>
     <definedName function="false" hidden="false" name="cqC_10" vbProcedure="false">In!$E$114</definedName>
+    <definedName function="false" hidden="false" name="cqC_10_hi" vbProcedure="false">In!$F$114</definedName>
+    <definedName function="false" hidden="false" name="cqC_10_lo" vbProcedure="false">In!$D$114</definedName>
     <definedName function="false" hidden="false" name="cqC_11" vbProcedure="false">In!$E$115</definedName>
+    <definedName function="false" hidden="false" name="cqC_11_hi" vbProcedure="false">In!$F$115</definedName>
+    <definedName function="false" hidden="false" name="cqC_11_lo" vbProcedure="false">In!$D$115</definedName>
     <definedName function="false" hidden="false" name="cqC_12" vbProcedure="false">In!$E$116</definedName>
+    <definedName function="false" hidden="false" name="cqC_12_hi" vbProcedure="false">In!$F$116</definedName>
+    <definedName function="false" hidden="false" name="cqC_12_lo" vbProcedure="false">In!$D$116</definedName>
     <definedName function="false" hidden="false" name="cqC_13" vbProcedure="false">In!$E$117</definedName>
+    <definedName function="false" hidden="false" name="cqC_13_hi" vbProcedure="false">In!$F$117</definedName>
+    <definedName function="false" hidden="false" name="cqC_13_lo" vbProcedure="false">In!$D$117</definedName>
     <definedName function="false" hidden="false" name="cqC_14" vbProcedure="false">In!$E$118</definedName>
+    <definedName function="false" hidden="false" name="cqC_14_hi" vbProcedure="false">In!$F$118</definedName>
+    <definedName function="false" hidden="false" name="cqC_14_lo" vbProcedure="false">In!$D$118</definedName>
     <definedName function="false" hidden="false" name="cqC_15" vbProcedure="false">In!$E$119</definedName>
+    <definedName function="false" hidden="false" name="cqC_15_hi" vbProcedure="false">In!$F$119</definedName>
+    <definedName function="false" hidden="false" name="cqC_15_lo" vbProcedure="false">In!$D$119</definedName>
     <definedName function="false" hidden="false" name="cqC_16" vbProcedure="false">In!$E$120</definedName>
+    <definedName function="false" hidden="false" name="cqC_16_hi" vbProcedure="false">In!$F$120</definedName>
+    <definedName function="false" hidden="false" name="cqC_16_lo" vbProcedure="false">In!$D$120</definedName>
     <definedName function="false" hidden="false" name="cqC_17" vbProcedure="false">In!$E$121</definedName>
+    <definedName function="false" hidden="false" name="cqC_17_hi" vbProcedure="false">In!$F$121</definedName>
+    <definedName function="false" hidden="false" name="cqC_17_lo" vbProcedure="false">In!$D$121</definedName>
     <definedName function="false" hidden="false" name="cqC_18" vbProcedure="false">In!$E$122</definedName>
+    <definedName function="false" hidden="false" name="cqC_18_hi" vbProcedure="false">In!$F$122</definedName>
+    <definedName function="false" hidden="false" name="cqC_18_lo" vbProcedure="false">In!$D$122</definedName>
     <definedName function="false" hidden="false" name="cqC_19" vbProcedure="false">In!$E$123</definedName>
+    <definedName function="false" hidden="false" name="cqC_19_hi" vbProcedure="false">In!$F$123</definedName>
+    <definedName function="false" hidden="false" name="cqC_19_lo" vbProcedure="false">In!$D$123</definedName>
     <definedName function="false" hidden="false" name="cqC_8" vbProcedure="false">In!$E$112</definedName>
+    <definedName function="false" hidden="false" name="cqC_8_hi" vbProcedure="false">In!$F$112</definedName>
+    <definedName function="false" hidden="false" name="cqC_8_lo" vbProcedure="false">In!$D$112</definedName>
     <definedName function="false" hidden="false" name="cqC_9" vbProcedure="false">In!$E$113</definedName>
+    <definedName function="false" hidden="false" name="cqC_9_hi" vbProcedure="false">In!$F$113</definedName>
+    <definedName function="false" hidden="false" name="cqC_9_lo" vbProcedure="false">In!$D$113</definedName>
     <definedName function="false" hidden="false" name="cq_1" vbProcedure="false">In!$E$81</definedName>
     <definedName function="false" hidden="false" name="cq_2" vbProcedure="false">In!$E$82</definedName>
     <definedName function="false" hidden="false" name="cq_3" vbProcedure="false">In!$E$83</definedName>
@@ -126,8 +150,14 @@
     <definedName function="false" hidden="false" name="fx_hi" vbProcedure="false">In!$F$5</definedName>
     <definedName function="false" hidden="false" name="fx_lo" vbProcedure="false">In!$D$5</definedName>
     <definedName function="false" hidden="false" name="g_amd_26" vbProcedure="false">In!$E$195</definedName>
+    <definedName function="false" hidden="false" name="g_amd_26_hi" vbProcedure="false">In!$F$195</definedName>
+    <definedName function="false" hidden="false" name="g_amd_26_lo" vbProcedure="false">In!$D$195</definedName>
     <definedName function="false" hidden="false" name="g_amd_27" vbProcedure="false">In!$E$196</definedName>
+    <definedName function="false" hidden="false" name="g_amd_27_hi" vbProcedure="false">In!$F$196</definedName>
+    <definedName function="false" hidden="false" name="g_amd_27_lo" vbProcedure="false">In!$D$196</definedName>
     <definedName function="false" hidden="false" name="g_amd_28" vbProcedure="false">In!$E$197</definedName>
+    <definedName function="false" hidden="false" name="g_amd_28_hi" vbProcedure="false">In!$F$197</definedName>
+    <definedName function="false" hidden="false" name="g_amd_28_lo" vbProcedure="false">In!$D$197</definedName>
     <definedName function="false" hidden="false" name="g_bw_26" vbProcedure="false">In!$E$171</definedName>
     <definedName function="false" hidden="false" name="g_bw_27" vbProcedure="false">In!$E$172</definedName>
     <definedName function="false" hidden="false" name="g_bw_28" vbProcedure="false">In!$E$173</definedName>
@@ -135,8 +165,14 @@
     <definedName function="false" hidden="false" name="g_hp_27" vbProcedure="false">In!$E$190</definedName>
     <definedName function="false" hidden="false" name="g_hp_28" vbProcedure="false">In!$E$191</definedName>
     <definedName function="false" hidden="false" name="g_oth_26" vbProcedure="false">In!$E$213</definedName>
+    <definedName function="false" hidden="false" name="g_oth_26_hi" vbProcedure="false">In!$F$213</definedName>
+    <definedName function="false" hidden="false" name="g_oth_26_lo" vbProcedure="false">In!$D$213</definedName>
     <definedName function="false" hidden="false" name="g_oth_27" vbProcedure="false">In!$E$214</definedName>
+    <definedName function="false" hidden="false" name="g_oth_27_hi" vbProcedure="false">In!$F$214</definedName>
+    <definedName function="false" hidden="false" name="g_oth_27_lo" vbProcedure="false">In!$D$214</definedName>
     <definedName function="false" hidden="false" name="g_oth_28" vbProcedure="false">In!$E$215</definedName>
+    <definedName function="false" hidden="false" name="g_oth_28_hi" vbProcedure="false">In!$F$215</definedName>
+    <definedName function="false" hidden="false" name="g_oth_28_lo" vbProcedure="false">In!$D$215</definedName>
     <definedName function="false" hidden="false" name="g_rb_26" vbProcedure="false">In!$E$177</definedName>
     <definedName function="false" hidden="false" name="g_rb_27" vbProcedure="false">In!$E$178</definedName>
     <definedName function="false" hidden="false" name="g_rb_28" vbProcedure="false">In!$E$179</definedName>
@@ -147,8 +183,14 @@
     <definedName function="false" hidden="false" name="g_tpu_27" vbProcedure="false">In!$E$202</definedName>
     <definedName function="false" hidden="false" name="g_tpu_28" vbProcedure="false">In!$E$203</definedName>
     <definedName function="false" hidden="false" name="g_trn_26" vbProcedure="false">In!$E$207</definedName>
+    <definedName function="false" hidden="false" name="g_trn_26_hi" vbProcedure="false">In!$F$207</definedName>
+    <definedName function="false" hidden="false" name="g_trn_26_lo" vbProcedure="false">In!$D$207</definedName>
     <definedName function="false" hidden="false" name="g_trn_27" vbProcedure="false">In!$E$208</definedName>
+    <definedName function="false" hidden="false" name="g_trn_27_hi" vbProcedure="false">In!$F$208</definedName>
+    <definedName function="false" hidden="false" name="g_trn_27_lo" vbProcedure="false">In!$D$208</definedName>
     <definedName function="false" hidden="false" name="g_trn_28" vbProcedure="false">In!$E$209</definedName>
+    <definedName function="false" hidden="false" name="g_trn_28_hi" vbProcedure="false">In!$F$209</definedName>
+    <definedName function="false" hidden="false" name="g_trn_28_lo" vbProcedure="false">In!$D$209</definedName>
     <definedName function="false" hidden="false" name="hbm_dem29" vbProcedure="false">In!$E$234</definedName>
     <definedName function="false" hidden="false" name="hbm_dem29_hi" vbProcedure="false">In!$F$234</definedName>
     <definedName function="false" hidden="false" name="hbm_dem29_lo" vbProcedure="false">In!$D$234</definedName>
@@ -250,17 +292,41 @@
     <definedName function="false" hidden="false" name="nqB_8" vbProcedure="false">In!$E$143</definedName>
     <definedName function="false" hidden="false" name="nqB_9" vbProcedure="false">In!$E$144</definedName>
     <definedName function="false" hidden="false" name="nqC_10" vbProcedure="false">In!$E$157</definedName>
+    <definedName function="false" hidden="false" name="nqC_10_hi" vbProcedure="false">In!$F$157</definedName>
+    <definedName function="false" hidden="false" name="nqC_10_lo" vbProcedure="false">In!$D$157</definedName>
     <definedName function="false" hidden="false" name="nqC_11" vbProcedure="false">In!$E$158</definedName>
+    <definedName function="false" hidden="false" name="nqC_11_hi" vbProcedure="false">In!$F$158</definedName>
+    <definedName function="false" hidden="false" name="nqC_11_lo" vbProcedure="false">In!$D$158</definedName>
     <definedName function="false" hidden="false" name="nqC_12" vbProcedure="false">In!$E$159</definedName>
+    <definedName function="false" hidden="false" name="nqC_12_hi" vbProcedure="false">In!$F$159</definedName>
+    <definedName function="false" hidden="false" name="nqC_12_lo" vbProcedure="false">In!$D$159</definedName>
     <definedName function="false" hidden="false" name="nqC_13" vbProcedure="false">In!$E$160</definedName>
+    <definedName function="false" hidden="false" name="nqC_13_hi" vbProcedure="false">In!$F$160</definedName>
+    <definedName function="false" hidden="false" name="nqC_13_lo" vbProcedure="false">In!$D$160</definedName>
     <definedName function="false" hidden="false" name="nqC_14" vbProcedure="false">In!$E$161</definedName>
+    <definedName function="false" hidden="false" name="nqC_14_hi" vbProcedure="false">In!$F$161</definedName>
+    <definedName function="false" hidden="false" name="nqC_14_lo" vbProcedure="false">In!$D$161</definedName>
     <definedName function="false" hidden="false" name="nqC_15" vbProcedure="false">In!$E$162</definedName>
+    <definedName function="false" hidden="false" name="nqC_15_hi" vbProcedure="false">In!$F$162</definedName>
+    <definedName function="false" hidden="false" name="nqC_15_lo" vbProcedure="false">In!$D$162</definedName>
     <definedName function="false" hidden="false" name="nqC_16" vbProcedure="false">In!$E$163</definedName>
+    <definedName function="false" hidden="false" name="nqC_16_hi" vbProcedure="false">In!$F$163</definedName>
+    <definedName function="false" hidden="false" name="nqC_16_lo" vbProcedure="false">In!$D$163</definedName>
     <definedName function="false" hidden="false" name="nqC_17" vbProcedure="false">In!$E$164</definedName>
+    <definedName function="false" hidden="false" name="nqC_17_hi" vbProcedure="false">In!$F$164</definedName>
+    <definedName function="false" hidden="false" name="nqC_17_lo" vbProcedure="false">In!$D$164</definedName>
     <definedName function="false" hidden="false" name="nqC_18" vbProcedure="false">In!$E$165</definedName>
+    <definedName function="false" hidden="false" name="nqC_18_hi" vbProcedure="false">In!$F$165</definedName>
+    <definedName function="false" hidden="false" name="nqC_18_lo" vbProcedure="false">In!$D$165</definedName>
     <definedName function="false" hidden="false" name="nqC_19" vbProcedure="false">In!$E$166</definedName>
+    <definedName function="false" hidden="false" name="nqC_19_hi" vbProcedure="false">In!$F$166</definedName>
+    <definedName function="false" hidden="false" name="nqC_19_lo" vbProcedure="false">In!$D$166</definedName>
     <definedName function="false" hidden="false" name="nqC_8" vbProcedure="false">In!$E$155</definedName>
+    <definedName function="false" hidden="false" name="nqC_8_hi" vbProcedure="false">In!$F$155</definedName>
+    <definedName function="false" hidden="false" name="nqC_8_lo" vbProcedure="false">In!$D$155</definedName>
     <definedName function="false" hidden="false" name="nqC_9" vbProcedure="false">In!$E$156</definedName>
+    <definedName function="false" hidden="false" name="nqC_9_hi" vbProcedure="false">In!$F$156</definedName>
+    <definedName function="false" hidden="false" name="nqC_9_lo" vbProcedure="false">In!$D$156</definedName>
     <definedName function="false" hidden="false" name="nq_1" vbProcedure="false">In!$E$124</definedName>
     <definedName function="false" hidden="false" name="nq_2" vbProcedure="false">In!$E$125</definedName>
     <definedName function="false" hidden="false" name="nq_3" vbProcedure="false">In!$E$126</definedName>
@@ -363,8 +429,14 @@
     <definedName function="false" hidden="false" name="um29_C_hi" vbProcedure="false">In!$F$222</definedName>
     <definedName function="false" hidden="false" name="um29_C_lo" vbProcedure="false">In!$D$222</definedName>
     <definedName function="false" hidden="false" name="u_amd_26" vbProcedure="false">In!$E$192</definedName>
+    <definedName function="false" hidden="false" name="u_amd_26_hi" vbProcedure="false">In!$F$192</definedName>
+    <definedName function="false" hidden="false" name="u_amd_26_lo" vbProcedure="false">In!$D$192</definedName>
     <definedName function="false" hidden="false" name="u_amd_27" vbProcedure="false">In!$E$193</definedName>
+    <definedName function="false" hidden="false" name="u_amd_27_hi" vbProcedure="false">In!$F$193</definedName>
+    <definedName function="false" hidden="false" name="u_amd_27_lo" vbProcedure="false">In!$D$193</definedName>
     <definedName function="false" hidden="false" name="u_amd_28" vbProcedure="false">In!$E$194</definedName>
+    <definedName function="false" hidden="false" name="u_amd_28_hi" vbProcedure="false">In!$F$194</definedName>
+    <definedName function="false" hidden="false" name="u_amd_28_lo" vbProcedure="false">In!$D$194</definedName>
     <definedName function="false" hidden="false" name="u_bw_26" vbProcedure="false">In!$E$168</definedName>
     <definedName function="false" hidden="false" name="u_bw_27" vbProcedure="false">In!$E$169</definedName>
     <definedName function="false" hidden="false" name="u_bw_28" vbProcedure="false">In!$E$170</definedName>
@@ -372,20 +444,38 @@
     <definedName function="false" hidden="false" name="u_hp_27" vbProcedure="false">In!$E$187</definedName>
     <definedName function="false" hidden="false" name="u_hp_28" vbProcedure="false">In!$E$188</definedName>
     <definedName function="false" hidden="false" name="u_oth_26" vbProcedure="false">In!$E$210</definedName>
+    <definedName function="false" hidden="false" name="u_oth_26_hi" vbProcedure="false">In!$F$210</definedName>
+    <definedName function="false" hidden="false" name="u_oth_26_lo" vbProcedure="false">In!$D$210</definedName>
     <definedName function="false" hidden="false" name="u_oth_27" vbProcedure="false">In!$E$211</definedName>
+    <definedName function="false" hidden="false" name="u_oth_27_hi" vbProcedure="false">In!$F$211</definedName>
+    <definedName function="false" hidden="false" name="u_oth_27_lo" vbProcedure="false">In!$D$211</definedName>
     <definedName function="false" hidden="false" name="u_oth_28" vbProcedure="false">In!$E$212</definedName>
+    <definedName function="false" hidden="false" name="u_oth_28_hi" vbProcedure="false">In!$F$212</definedName>
+    <definedName function="false" hidden="false" name="u_oth_28_lo" vbProcedure="false">In!$D$212</definedName>
     <definedName function="false" hidden="false" name="u_rb_26" vbProcedure="false">In!$E$174</definedName>
     <definedName function="false" hidden="false" name="u_rb_27" vbProcedure="false">In!$E$175</definedName>
     <definedName function="false" hidden="false" name="u_rb_28" vbProcedure="false">In!$E$176</definedName>
     <definedName function="false" hidden="false" name="u_ru_26" vbProcedure="false">In!$E$180</definedName>
+    <definedName function="false" hidden="false" name="u_ru_26_hi" vbProcedure="false">In!$F$180</definedName>
+    <definedName function="false" hidden="false" name="u_ru_26_lo" vbProcedure="false">In!$D$180</definedName>
     <definedName function="false" hidden="false" name="u_ru_27" vbProcedure="false">In!$E$181</definedName>
+    <definedName function="false" hidden="false" name="u_ru_27_hi" vbProcedure="false">In!$F$181</definedName>
+    <definedName function="false" hidden="false" name="u_ru_27_lo" vbProcedure="false">In!$D$181</definedName>
     <definedName function="false" hidden="false" name="u_ru_28" vbProcedure="false">In!$E$182</definedName>
+    <definedName function="false" hidden="false" name="u_ru_28_hi" vbProcedure="false">In!$F$182</definedName>
+    <definedName function="false" hidden="false" name="u_ru_28_lo" vbProcedure="false">In!$D$182</definedName>
     <definedName function="false" hidden="false" name="u_tpu_26" vbProcedure="false">In!$E$198</definedName>
     <definedName function="false" hidden="false" name="u_tpu_27" vbProcedure="false">In!$E$199</definedName>
     <definedName function="false" hidden="false" name="u_tpu_28" vbProcedure="false">In!$E$200</definedName>
     <definedName function="false" hidden="false" name="u_trn_26" vbProcedure="false">In!$E$204</definedName>
+    <definedName function="false" hidden="false" name="u_trn_26_hi" vbProcedure="false">In!$F$204</definedName>
+    <definedName function="false" hidden="false" name="u_trn_26_lo" vbProcedure="false">In!$D$204</definedName>
     <definedName function="false" hidden="false" name="u_trn_27" vbProcedure="false">In!$E$205</definedName>
+    <definedName function="false" hidden="false" name="u_trn_27_hi" vbProcedure="false">In!$F$205</definedName>
+    <definedName function="false" hidden="false" name="u_trn_27_lo" vbProcedure="false">In!$D$205</definedName>
     <definedName function="false" hidden="false" name="u_trn_28" vbProcedure="false">In!$E$206</definedName>
+    <definedName function="false" hidden="false" name="u_trn_28_hi" vbProcedure="false">In!$F$206</definedName>
+    <definedName function="false" hidden="false" name="u_trn_28_lo" vbProcedure="false">In!$D$206</definedName>
     <definedName function="false" hidden="false" name="w_c" vbProcedure="false">In!$E$35</definedName>
     <definedName function="false" hidden="false" name="w_h" vbProcedure="false">In!$E$36</definedName>
     <definedName function="false" hidden="false" name="w_n" vbProcedure="false">In!$E$37</definedName>
@@ -400,7 +490,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2037" uniqueCount="1063">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2039" uniqueCount="1066">
   <si>
     <r>
       <rPr>
@@ -11012,7 +11102,121 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">自谷底回升</t>
+      <t xml:space="preserve">自谷底回升。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±5pt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028–29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±10pt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，表示路徑形狀的不確定（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），不是另一個情境</t>
     </r>
   </si>
   <si>
@@ -13894,7 +14098,121 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年水準</t>
+      <t xml:space="preserve">年水準。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±5pt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028–29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各季 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±10pt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，表示路徑形狀的不確定（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），不是另一個情境</t>
     </r>
   </si>
   <si>
@@ -15697,7 +16015,83 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">／封裝</t>
+      <t xml:space="preserve">／封裝。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 0–0.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 1.0–3.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：時程提前／延後一年）</t>
     </r>
   </si>
   <si>
@@ -15803,6 +16197,122 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NVIDIA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rubin Ultra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">每封裝 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 TB HBM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（產品路線圖，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">標記由 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Interested-party</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：規格為公司公布，不是假設）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">g_ru_27</t>
   </si>
   <si>
@@ -16352,6 +16862,148 @@
       </rPr>
       <t xml:space="preserve">Assumed</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 0.6–0.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 1.2–1.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 1.5–2.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；每顆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MI355X 288</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MI450 432 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為上下限</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">u_amd_27</t>
@@ -16964,6 +17616,167 @@
       </rPr>
       <t xml:space="preserve">Trn3 144</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 1.5–2.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 2.0–3.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 2.0–4.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；每顆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Trn2 96</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Trn3 144</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、下一代 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">256 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為界</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">u_trn_27</t>
@@ -17264,6 +18077,101 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">JPMorgan ASIC 12.5M − TPU − Trainium</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。區間（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）：顆數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 0.5–1.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 3.0–6.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 3.5–7.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；每顆 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM ±50 GB</t>
     </r>
   </si>
   <si>
@@ -18161,7 +19069,178 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">測試機需求用同一組係數</t>
+      <t xml:space="preserve">測試機需求用同一組係數。情境 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為定義值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">標記由 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Derived</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仍為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，區間 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±0.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
@@ -19864,6 +20943,84 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2029 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無外部預測；供給新廠（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、龍仁、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M15X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）投產下單價緩降</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">hbm_p29_B</t>
   </si>
   <si>
@@ -19923,6 +21080,65 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2029 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無外部預測；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已下修後持平</t>
     </r>
   </si>
   <si>
@@ -36270,24 +37486,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">nv_hbm</f>
         <v>4.46</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B4" s="0" t="str">
         <f aca="false">TEXT(Mkt!D16,"0")&amp;" ／ "&amp;TEXT(Mkt!E16,"0")</f>
@@ -36299,37 +37515,37 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="B5" s="0" t="str">
         <f aca="false">TEXT(Mkt!D33,"0")&amp;" ／ "&amp;TEXT(Mkt!E33,"0")</f>
         <v>55 ／ 154</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="B6" s="14" t="n">
         <f aca="false">Mkt!E27</f>
         <v>1.23255275</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
     </row>
   </sheetData>
@@ -36357,111 +37573,111 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
   </sheetData>
@@ -38730,8 +39946,14 @@
       <c r="C112" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D112" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E112" s="7" t="n">
         <v>0.05</v>
+      </c>
+      <c r="F112" s="7" t="n">
+        <v>0.1</v>
       </c>
       <c r="G112" s="8" t="s">
         <v>61</v>
@@ -38750,8 +39972,14 @@
       <c r="C113" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D113" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E113" s="7" t="n">
         <v>0.02</v>
+      </c>
+      <c r="F113" s="7" t="n">
+        <v>0.07</v>
       </c>
       <c r="G113" s="8" t="s">
         <v>61</v>
@@ -38770,8 +39998,14 @@
       <c r="C114" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D114" s="7" t="n">
+        <v>-0.13</v>
+      </c>
       <c r="E114" s="7" t="n">
         <v>-0.08</v>
+      </c>
+      <c r="F114" s="7" t="n">
+        <v>-0.03</v>
       </c>
       <c r="G114" s="8" t="s">
         <v>61</v>
@@ -38790,8 +40024,14 @@
       <c r="C115" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D115" s="7" t="n">
+        <v>-0.2</v>
+      </c>
       <c r="E115" s="7" t="n">
         <v>-0.15</v>
+      </c>
+      <c r="F115" s="7" t="n">
+        <v>-0.1</v>
       </c>
       <c r="G115" s="8" t="s">
         <v>61</v>
@@ -38810,8 +40050,14 @@
       <c r="C116" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D116" s="7" t="n">
+        <v>-0.45</v>
+      </c>
       <c r="E116" s="7" t="n">
         <v>-0.35</v>
+      </c>
+      <c r="F116" s="7" t="n">
+        <v>-0.25</v>
       </c>
       <c r="G116" s="8" t="s">
         <v>61</v>
@@ -38830,8 +40076,14 @@
       <c r="C117" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D117" s="7" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="E117" s="7" t="n">
         <v>-0.3</v>
+      </c>
+      <c r="F117" s="7" t="n">
+        <v>-0.2</v>
       </c>
       <c r="G117" s="8" t="s">
         <v>61</v>
@@ -38850,8 +40102,14 @@
       <c r="C118" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D118" s="7" t="n">
+        <v>-0.35</v>
+      </c>
       <c r="E118" s="7" t="n">
         <v>-0.25</v>
+      </c>
+      <c r="F118" s="7" t="n">
+        <v>-0.15</v>
       </c>
       <c r="G118" s="8" t="s">
         <v>61</v>
@@ -38870,8 +40128,14 @@
       <c r="C119" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D119" s="7" t="n">
+        <v>-0.3</v>
+      </c>
       <c r="E119" s="7" t="n">
         <v>-0.2</v>
+      </c>
+      <c r="F119" s="7" t="n">
+        <v>-0.1</v>
       </c>
       <c r="G119" s="8" t="s">
         <v>61</v>
@@ -38890,8 +40154,14 @@
       <c r="C120" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D120" s="7" t="n">
+        <v>-0.1</v>
+      </c>
       <c r="E120" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="F120" s="7" t="n">
+        <v>0.1</v>
       </c>
       <c r="G120" s="8" t="s">
         <v>61</v>
@@ -38910,8 +40180,14 @@
       <c r="C121" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D121" s="7" t="n">
+        <v>-0.05</v>
+      </c>
       <c r="E121" s="7" t="n">
         <v>0.05</v>
+      </c>
+      <c r="F121" s="7" t="n">
+        <v>0.15</v>
       </c>
       <c r="G121" s="8" t="s">
         <v>61</v>
@@ -38930,8 +40206,14 @@
       <c r="C122" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D122" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E122" s="7" t="n">
         <v>0.08</v>
+      </c>
+      <c r="F122" s="7" t="n">
+        <v>0.18</v>
       </c>
       <c r="G122" s="8" t="s">
         <v>61</v>
@@ -38950,8 +40232,14 @@
       <c r="C123" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D123" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E123" s="7" t="n">
         <v>0.1</v>
+      </c>
+      <c r="F123" s="7" t="n">
+        <v>0.2</v>
       </c>
       <c r="G123" s="8" t="s">
         <v>61</v>
@@ -39590,8 +40878,14 @@
       <c r="C155" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D155" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E155" s="7" t="n">
         <v>0.05</v>
+      </c>
+      <c r="F155" s="7" t="n">
+        <v>0.1</v>
       </c>
       <c r="G155" s="8" t="s">
         <v>61</v>
@@ -39610,8 +40904,14 @@
       <c r="C156" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D156" s="7" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="E156" s="7" t="n">
         <v>0.02</v>
+      </c>
+      <c r="F156" s="7" t="n">
+        <v>0.07</v>
       </c>
       <c r="G156" s="8" t="s">
         <v>61</v>
@@ -39630,8 +40930,14 @@
       <c r="C157" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D157" s="7" t="n">
+        <v>-0.15</v>
+      </c>
       <c r="E157" s="7" t="n">
         <v>-0.1</v>
+      </c>
+      <c r="F157" s="7" t="n">
+        <v>-0.05</v>
       </c>
       <c r="G157" s="8" t="s">
         <v>61</v>
@@ -39650,8 +40956,14 @@
       <c r="C158" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D158" s="7" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="E158" s="7" t="n">
         <v>-0.2</v>
+      </c>
+      <c r="F158" s="7" t="n">
+        <v>-0.15</v>
       </c>
       <c r="G158" s="8" t="s">
         <v>61</v>
@@ -39670,8 +40982,14 @@
       <c r="C159" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D159" s="7" t="n">
+        <v>-0.45</v>
+      </c>
       <c r="E159" s="7" t="n">
         <v>-0.35</v>
+      </c>
+      <c r="F159" s="7" t="n">
+        <v>-0.25</v>
       </c>
       <c r="G159" s="8" t="s">
         <v>61</v>
@@ -39690,8 +41008,14 @@
       <c r="C160" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D160" s="7" t="n">
+        <v>-0.45</v>
+      </c>
       <c r="E160" s="7" t="n">
         <v>-0.35</v>
+      </c>
+      <c r="F160" s="7" t="n">
+        <v>-0.25</v>
       </c>
       <c r="G160" s="8" t="s">
         <v>61</v>
@@ -39710,8 +41034,14 @@
       <c r="C161" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D161" s="7" t="n">
+        <v>-0.35</v>
+      </c>
       <c r="E161" s="7" t="n">
         <v>-0.25</v>
+      </c>
+      <c r="F161" s="7" t="n">
+        <v>-0.15</v>
       </c>
       <c r="G161" s="8" t="s">
         <v>61</v>
@@ -39730,8 +41060,14 @@
       <c r="C162" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D162" s="7" t="n">
+        <v>-0.3</v>
+      </c>
       <c r="E162" s="7" t="n">
         <v>-0.2</v>
+      </c>
+      <c r="F162" s="7" t="n">
+        <v>-0.1</v>
       </c>
       <c r="G162" s="8" t="s">
         <v>61</v>
@@ -39750,8 +41086,14 @@
       <c r="C163" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D163" s="7" t="n">
+        <v>-0.1</v>
+      </c>
       <c r="E163" s="7" t="n">
         <v>0</v>
+      </c>
+      <c r="F163" s="7" t="n">
+        <v>0.1</v>
       </c>
       <c r="G163" s="8" t="s">
         <v>61</v>
@@ -39770,8 +41112,14 @@
       <c r="C164" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D164" s="7" t="n">
+        <v>-0.05</v>
+      </c>
       <c r="E164" s="7" t="n">
         <v>0.05</v>
+      </c>
+      <c r="F164" s="7" t="n">
+        <v>0.15</v>
       </c>
       <c r="G164" s="8" t="s">
         <v>61</v>
@@ -39790,8 +41138,14 @@
       <c r="C165" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D165" s="7" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="E165" s="7" t="n">
         <v>0.08</v>
+      </c>
+      <c r="F165" s="7" t="n">
+        <v>0.18</v>
       </c>
       <c r="G165" s="8" t="s">
         <v>61</v>
@@ -39810,8 +41164,14 @@
       <c r="C166" s="0" t="s">
         <v>48</v>
       </c>
+      <c r="D166" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E166" s="7" t="n">
         <v>0.1</v>
+      </c>
+      <c r="F166" s="7" t="n">
+        <v>0.2</v>
       </c>
       <c r="G166" s="8" t="s">
         <v>61</v>
@@ -40075,7 +41435,13 @@
       <c r="C180" s="4" t="s">
         <v>421</v>
       </c>
+      <c r="D180" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E180" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G180" s="8" t="s">
@@ -40095,8 +41461,14 @@
       <c r="C181" s="4" t="s">
         <v>421</v>
       </c>
+      <c r="D181" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E181" s="7" t="n">
         <v>0.3</v>
+      </c>
+      <c r="F181" s="7" t="n">
+        <v>0.6</v>
       </c>
       <c r="G181" s="8" t="s">
         <v>61</v>
@@ -40115,8 +41487,14 @@
       <c r="C182" s="4" t="s">
         <v>421</v>
       </c>
+      <c r="D182" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="E182" s="7" t="n">
         <v>2</v>
+      </c>
+      <c r="F182" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="G182" s="8" t="s">
         <v>61</v>
@@ -40139,18 +41517,18 @@
         <v>1024</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H183" s="4" t="s">
-        <v>210</v>
+        <v>65</v>
+      </c>
+      <c r="H183" s="8" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B184" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C184" s="0" t="s">
         <v>429</v>
@@ -40159,7 +41537,7 @@
         <v>1024</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H184" s="4" t="s">
         <v>210</v>
@@ -40167,10 +41545,10 @@
     </row>
     <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B185" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C185" s="0" t="s">
         <v>429</v>
@@ -40179,7 +41557,7 @@
         <v>1024</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H185" s="4" t="s">
         <v>210</v>
@@ -40187,10 +41565,10 @@
     </row>
     <row r="186" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B186" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>421</v>
@@ -40202,15 +41580,15 @@
         <v>65</v>
       </c>
       <c r="H186" s="8" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B187" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>421</v>
@@ -40227,10 +41605,10 @@
     </row>
     <row r="188" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B188" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>421</v>
@@ -40247,10 +41625,10 @@
     </row>
     <row r="189" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B189" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C189" s="0" t="s">
         <v>429</v>
@@ -40267,10 +41645,10 @@
     </row>
     <row r="190" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B190" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C190" s="0" t="s">
         <v>429</v>
@@ -40287,10 +41665,10 @@
     </row>
     <row r="191" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B191" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C191" s="0" t="s">
         <v>429</v>
@@ -40307,39 +41685,51 @@
     </row>
     <row r="192" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B192" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>421</v>
       </c>
+      <c r="D192" s="7" t="n">
+        <v>0.6</v>
+      </c>
       <c r="E192" s="7" t="n">
         <v>0.75</v>
       </c>
+      <c r="F192" s="7" t="n">
+        <v>0.9</v>
+      </c>
       <c r="G192" s="8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H192" s="8" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B193" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>421</v>
       </c>
+      <c r="D193" s="7" t="n">
+        <v>1.2</v>
+      </c>
       <c r="E193" s="7" t="n">
         <v>1.5</v>
       </c>
+      <c r="F193" s="7" t="n">
+        <v>1.8</v>
+      </c>
       <c r="G193" s="8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H193" s="4" t="s">
         <v>210</v>
@@ -40347,19 +41737,25 @@
     </row>
     <row r="194" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B194" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>421</v>
       </c>
+      <c r="D194" s="7" t="n">
+        <v>1.5</v>
+      </c>
       <c r="E194" s="7" t="n">
         <v>2</v>
       </c>
+      <c r="F194" s="7" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G194" s="8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H194" s="4" t="s">
         <v>210</v>
@@ -40367,19 +41763,25 @@
     </row>
     <row r="195" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B195" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C195" s="0" t="s">
         <v>429</v>
       </c>
+      <c r="D195" s="7" t="n">
+        <v>288</v>
+      </c>
       <c r="E195" s="7" t="n">
         <v>288</v>
       </c>
+      <c r="F195" s="7" t="n">
+        <v>288</v>
+      </c>
       <c r="G195" s="8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H195" s="4" t="s">
         <v>210</v>
@@ -40387,19 +41789,25 @@
     </row>
     <row r="196" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B196" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C196" s="0" t="s">
         <v>429</v>
       </c>
+      <c r="D196" s="7" t="n">
+        <v>288</v>
+      </c>
       <c r="E196" s="7" t="n">
         <v>360</v>
       </c>
+      <c r="F196" s="7" t="n">
+        <v>432</v>
+      </c>
       <c r="G196" s="8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H196" s="4" t="s">
         <v>210</v>
@@ -40407,19 +41815,25 @@
     </row>
     <row r="197" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B197" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C197" s="0" t="s">
         <v>429</v>
       </c>
+      <c r="D197" s="7" t="n">
+        <v>432</v>
+      </c>
       <c r="E197" s="7" t="n">
         <v>432</v>
       </c>
+      <c r="F197" s="7" t="n">
+        <v>432</v>
+      </c>
       <c r="G197" s="8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H197" s="4" t="s">
         <v>210</v>
@@ -40427,10 +41841,10 @@
     </row>
     <row r="198" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B198" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>421</v>
@@ -40442,15 +41856,15 @@
         <v>65</v>
       </c>
       <c r="H198" s="8" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B199" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C199" s="4" t="s">
         <v>421</v>
@@ -40467,10 +41881,10 @@
     </row>
     <row r="200" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B200" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>421</v>
@@ -40487,10 +41901,10 @@
     </row>
     <row r="201" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B201" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C201" s="0" t="s">
         <v>429</v>
@@ -40507,10 +41921,10 @@
     </row>
     <row r="202" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B202" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C202" s="0" t="s">
         <v>429</v>
@@ -40527,10 +41941,10 @@
     </row>
     <row r="203" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B203" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C203" s="0" t="s">
         <v>429</v>
@@ -40547,37 +41961,49 @@
     </row>
     <row r="204" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B204" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>421</v>
       </c>
+      <c r="D204" s="7" t="n">
+        <v>1.5</v>
+      </c>
       <c r="E204" s="7" t="n">
         <v>2</v>
       </c>
+      <c r="F204" s="7" t="n">
+        <v>2.5</v>
+      </c>
       <c r="G204" s="8" t="s">
         <v>61</v>
       </c>
       <c r="H204" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B205" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>421</v>
       </c>
+      <c r="D205" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="E205" s="7" t="n">
         <v>2.5</v>
       </c>
+      <c r="F205" s="7" t="n">
+        <v>3.5</v>
+      </c>
       <c r="G205" s="8" t="s">
         <v>61</v>
       </c>
@@ -40587,17 +42013,23 @@
     </row>
     <row r="206" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B206" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>421</v>
       </c>
+      <c r="D206" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="E206" s="7" t="n">
         <v>3</v>
       </c>
+      <c r="F206" s="7" t="n">
+        <v>4</v>
+      </c>
       <c r="G206" s="8" t="s">
         <v>61</v>
       </c>
@@ -40607,17 +42039,23 @@
     </row>
     <row r="207" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B207" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C207" s="0" t="s">
         <v>429</v>
       </c>
+      <c r="D207" s="7" t="n">
+        <v>96</v>
+      </c>
       <c r="E207" s="7" t="n">
         <v>110</v>
       </c>
+      <c r="F207" s="7" t="n">
+        <v>144</v>
+      </c>
       <c r="G207" s="8" t="s">
         <v>61</v>
       </c>
@@ -40627,17 +42065,23 @@
     </row>
     <row r="208" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B208" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C208" s="0" t="s">
         <v>429</v>
       </c>
+      <c r="D208" s="7" t="n">
+        <v>120</v>
+      </c>
       <c r="E208" s="7" t="n">
         <v>144</v>
       </c>
+      <c r="F208" s="7" t="n">
+        <v>144</v>
+      </c>
       <c r="G208" s="8" t="s">
         <v>61</v>
       </c>
@@ -40647,17 +42091,23 @@
     </row>
     <row r="209" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B209" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C209" s="0" t="s">
         <v>429</v>
       </c>
+      <c r="D209" s="7" t="n">
+        <v>144</v>
+      </c>
       <c r="E209" s="7" t="n">
         <v>200</v>
       </c>
+      <c r="F209" s="7" t="n">
+        <v>256</v>
+      </c>
       <c r="G209" s="8" t="s">
         <v>61</v>
       </c>
@@ -40667,37 +42117,49 @@
     </row>
     <row r="210" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>421</v>
       </c>
+      <c r="D210" s="7" t="n">
+        <v>0.5</v>
+      </c>
       <c r="E210" s="7" t="n">
         <v>1</v>
       </c>
+      <c r="F210" s="7" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G210" s="8" t="s">
         <v>148</v>
       </c>
       <c r="H210" s="8" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>421</v>
       </c>
+      <c r="D211" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="E211" s="7" t="n">
         <v>4.5</v>
       </c>
+      <c r="F211" s="7" t="n">
+        <v>6</v>
+      </c>
       <c r="G211" s="8" t="s">
         <v>148</v>
       </c>
@@ -40707,17 +42169,23 @@
     </row>
     <row r="212" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>421</v>
       </c>
+      <c r="D212" s="7" t="n">
+        <v>3.5</v>
+      </c>
       <c r="E212" s="7" t="n">
         <v>5</v>
       </c>
+      <c r="F212" s="7" t="n">
+        <v>7</v>
+      </c>
       <c r="G212" s="8" t="s">
         <v>148</v>
       </c>
@@ -40727,17 +42195,23 @@
     </row>
     <row r="213" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C213" s="0" t="s">
         <v>429</v>
       </c>
+      <c r="D213" s="7" t="n">
+        <v>100</v>
+      </c>
       <c r="E213" s="7" t="n">
         <v>150</v>
       </c>
+      <c r="F213" s="7" t="n">
+        <v>200</v>
+      </c>
       <c r="G213" s="8" t="s">
         <v>148</v>
       </c>
@@ -40747,17 +42221,23 @@
     </row>
     <row r="214" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C214" s="0" t="s">
         <v>429</v>
       </c>
+      <c r="D214" s="7" t="n">
+        <v>150</v>
+      </c>
       <c r="E214" s="7" t="n">
         <v>200</v>
       </c>
+      <c r="F214" s="7" t="n">
+        <v>250</v>
+      </c>
       <c r="G214" s="8" t="s">
         <v>148</v>
       </c>
@@ -40767,17 +42247,23 @@
     </row>
     <row r="215" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C215" s="0" t="s">
         <v>429</v>
       </c>
+      <c r="D215" s="7" t="n">
+        <v>200</v>
+      </c>
       <c r="E215" s="7" t="n">
         <v>250</v>
       </c>
+      <c r="F215" s="7" t="n">
+        <v>300</v>
+      </c>
       <c r="G215" s="8" t="s">
         <v>148</v>
       </c>
@@ -40787,15 +42273,15 @@
     </row>
     <row r="216" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="6" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C217" s="0" t="s">
         <v>222</v>
@@ -40804,18 +42290,18 @@
         <v>1</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="H217" s="8" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C218" s="0" t="s">
         <v>222</v>
@@ -40824,7 +42310,7 @@
         <v>1</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="H218" s="4" t="s">
         <v>210</v>
@@ -40832,10 +42318,10 @@
     </row>
     <row r="219" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C219" s="0" t="s">
         <v>222</v>
@@ -40858,10 +42344,10 @@
     </row>
     <row r="220" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C220" s="0" t="s">
         <v>222</v>
@@ -40884,10 +42370,10 @@
     </row>
     <row r="221" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C221" s="0" t="s">
         <v>222</v>
@@ -40910,10 +42396,10 @@
     </row>
     <row r="222" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C222" s="0" t="s">
         <v>222</v>
@@ -40936,18 +42422,18 @@
     </row>
     <row r="223" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="6" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B224" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D224" s="7" t="n">
         <v>34</v>
@@ -40962,15 +42448,15 @@
         <v>43</v>
       </c>
       <c r="H224" s="8" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B225" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C225" s="0" t="s">
         <v>48</v>
@@ -40988,15 +42474,15 @@
         <v>65</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C226" s="0" t="s">
         <v>222</v>
@@ -41014,15 +42500,15 @@
         <v>61</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B227" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C227" s="0" t="s">
         <v>48</v>
@@ -41040,15 +42526,15 @@
         <v>65</v>
       </c>
       <c r="H227" s="8" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B228" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C228" s="0" t="s">
         <v>48</v>
@@ -41066,18 +42552,18 @@
         <v>61</v>
       </c>
       <c r="H228" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B229" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C229" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D229" s="7" t="n">
         <v>12.5</v>
@@ -41092,15 +42578,15 @@
         <v>65</v>
       </c>
       <c r="H229" s="8" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B230" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C230" s="0" t="s">
         <v>48</v>
@@ -41118,15 +42604,15 @@
         <v>65</v>
       </c>
       <c r="H230" s="8" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B231" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C231" s="0" t="s">
         <v>48</v>
@@ -41144,15 +42630,15 @@
         <v>65</v>
       </c>
       <c r="H231" s="8" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B232" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C232" s="0" t="s">
         <v>48</v>
@@ -41170,15 +42656,15 @@
         <v>61</v>
       </c>
       <c r="H232" s="4" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B233" s="0" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C233" s="0" t="s">
         <v>48</v>
@@ -41196,15 +42682,15 @@
         <v>61</v>
       </c>
       <c r="H233" s="4" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B234" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C234" s="0" t="s">
         <v>48</v>
@@ -41222,15 +42708,15 @@
         <v>61</v>
       </c>
       <c r="H234" s="8" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B235" s="0" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C235" s="0" t="s">
         <v>48</v>
@@ -41248,15 +42734,15 @@
         <v>61</v>
       </c>
       <c r="H235" s="8" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B236" s="0" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C236" s="0" t="s">
         <v>48</v>
@@ -41273,13 +42759,16 @@
       <c r="G236" s="8" t="s">
         <v>61</v>
       </c>
+      <c r="H236" s="8" t="s">
+        <v>582</v>
+      </c>
     </row>
     <row r="237" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="0" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B237" s="0" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C237" s="0" t="s">
         <v>48</v>
@@ -41296,13 +42785,16 @@
       <c r="G237" s="8" t="s">
         <v>61</v>
       </c>
+      <c r="H237" s="8" t="s">
+        <v>585</v>
+      </c>
     </row>
     <row r="238" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="0" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B238" s="0" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C238" s="0" t="s">
         <v>48</v>
@@ -41320,23 +42812,23 @@
         <v>61</v>
       </c>
       <c r="H238" s="4" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="6" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="0" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B240" s="0" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D240" s="7" t="n">
         <v>340</v>
@@ -41348,21 +42840,21 @@
         <v>400</v>
       </c>
       <c r="G240" s="8" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="H240" s="8" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="0" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D241" s="7" t="n">
         <v>38</v>
@@ -41377,18 +42869,18 @@
         <v>38</v>
       </c>
       <c r="H241" s="8" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="0" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B242" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="C242" s="0" t="s">
         <v>596</v>
-      </c>
-      <c r="C242" s="0" t="s">
-        <v>593</v>
       </c>
       <c r="D242" s="7" t="n">
         <v>3.5</v>
@@ -41403,18 +42895,18 @@
         <v>38</v>
       </c>
       <c r="H242" s="8" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="0" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C243" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E243" s="7" t="n">
         <v>54.6</v>
@@ -41423,18 +42915,18 @@
         <v>65</v>
       </c>
       <c r="H243" s="8" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="0" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C244" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E244" s="7" t="n">
         <v>77.4</v>
@@ -41443,18 +42935,18 @@
         <v>65</v>
       </c>
       <c r="H244" s="8" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="0" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E245" s="7" t="n">
         <v>152.8</v>
@@ -41463,20 +42955,20 @@
         <v>65</v>
       </c>
       <c r="H245" s="8" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="9" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C247" s="9" t="s">
         <v>48</v>
@@ -41490,15 +42982,15 @@
         <v>61</v>
       </c>
       <c r="H247" s="9" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="9" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C248" s="9" t="s">
         <v>48</v>
@@ -41512,15 +43004,15 @@
         <v>61</v>
       </c>
       <c r="H248" s="9" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="9" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C249" s="9" t="s">
         <v>48</v>
@@ -41534,15 +43026,15 @@
         <v>61</v>
       </c>
       <c r="H249" s="9" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="9" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C250" s="9" t="s">
         <v>48</v>
@@ -41556,15 +43048,15 @@
         <v>61</v>
       </c>
       <c r="H250" s="9" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="9" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B251" s="10" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C251" s="9" t="s">
         <v>48</v>
@@ -41578,15 +43070,15 @@
         <v>61</v>
       </c>
       <c r="H251" s="9" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="9" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B252" s="9" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C252" s="9" t="s">
         <v>48</v>
@@ -41601,15 +43093,15 @@
         <v>38</v>
       </c>
       <c r="H252" s="9" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="9" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B253" s="10" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C253" s="9" t="s">
         <v>48</v>
@@ -41623,15 +43115,15 @@
         <v>61</v>
       </c>
       <c r="H253" s="9" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="9" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B254" s="10" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C254" s="9" t="s">
         <v>48</v>
@@ -41646,15 +43138,15 @@
         <v>38</v>
       </c>
       <c r="H254" s="9" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="9" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B255" s="10" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C255" s="9" t="s">
         <v>48</v>
@@ -41669,15 +43161,15 @@
         <v>61</v>
       </c>
       <c r="H255" s="10" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="9" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B256" s="10" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C256" s="9" t="s">
         <v>48</v>
@@ -41692,15 +43184,15 @@
         <v>61</v>
       </c>
       <c r="H256" s="10" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="9" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B257" s="10" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C257" s="9" t="s">
         <v>48</v>
@@ -41715,15 +43207,15 @@
         <v>61</v>
       </c>
       <c r="H257" s="10" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="9" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B258" s="10" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C258" s="9" t="s">
         <v>222</v>
@@ -41737,15 +43229,15 @@
         <v>61</v>
       </c>
       <c r="H258" s="9" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="9" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B259" s="10" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C259" s="9" t="s">
         <v>222</v>
@@ -41759,15 +43251,15 @@
         <v>61</v>
       </c>
       <c r="H259" s="9" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="9" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="B260" s="10" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="C260" s="9" t="s">
         <v>48</v>
@@ -41782,15 +43274,15 @@
         <v>38</v>
       </c>
       <c r="H260" s="9" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="9" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B261" s="10" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C261" s="9" t="s">
         <v>48</v>
@@ -41805,15 +43297,15 @@
         <v>38</v>
       </c>
       <c r="H261" s="9" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="9" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B262" s="10" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C262" s="9" t="s">
         <v>48</v>
@@ -41828,15 +43320,15 @@
         <v>38</v>
       </c>
       <c r="H262" s="9" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="9" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B263" s="10" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C263" s="9" t="s">
         <v>42</v>
@@ -41854,15 +43346,15 @@
         <v>65</v>
       </c>
       <c r="H263" s="9" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="9" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B264" s="10" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C264" s="9" t="s">
         <v>42</v>
@@ -41876,15 +43368,15 @@
         <v>65</v>
       </c>
       <c r="H264" s="9" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="9" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B265" s="10" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C265" s="9" t="s">
         <v>42</v>
@@ -41898,15 +43390,15 @@
         <v>65</v>
       </c>
       <c r="H265" s="9" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="9" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="B266" s="10" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C266" s="9" t="s">
         <v>42</v>
@@ -41920,7 +43412,7 @@
         <v>65</v>
       </c>
       <c r="H266" s="9" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>
@@ -41948,83 +43440,83 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="P3" s="13" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="Q3" s="13" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="U3" s="13" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="V3" s="13" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>1</v>
@@ -42108,10 +43600,10 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>1</v>
@@ -42195,10 +43687,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>1</v>
@@ -42282,10 +43774,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
+        <v>690</v>
+      </c>
+      <c r="B8" s="0" t="s">
         <v>687</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>684</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>1</v>
@@ -42369,10 +43861,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>1</v>
@@ -42456,10 +43948,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C10" s="0" t="n">
         <v>1</v>
@@ -42543,50 +44035,50 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C14" s="14" t="n">
         <f aca="false">AVERAGE(C4:F4)</f>
@@ -42627,10 +44119,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C15" s="14" t="n">
         <f aca="false">AVERAGE(C5:F5)</f>
@@ -42671,10 +44163,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">AVERAGE(C6:F6)</f>
@@ -42715,10 +44207,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
+        <v>690</v>
+      </c>
+      <c r="B17" s="0" t="s">
         <v>687</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>684</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">AVERAGE(C8:F8)</f>
@@ -42759,10 +44251,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C18" s="14" t="n">
         <f aca="false">AVERAGE(C9:F9)</f>
@@ -42803,10 +44295,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C19" s="14" t="n">
         <f aca="false">AVERAGE(C10:F10)</f>
@@ -42871,7 +44363,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42882,35 +44374,35 @@
         <v>28</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D5" s="16" t="n">
         <f aca="false">u_bw_26*g_bw_26</f>
@@ -42927,10 +44419,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D6" s="16" t="n">
         <f aca="false">u_rb_26*g_rb_26</f>
@@ -42947,10 +44439,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D7" s="16" t="n">
         <f aca="false">u_ru_26*g_ru_26</f>
@@ -42967,10 +44459,10 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
+        <v>708</v>
+      </c>
+      <c r="B8" s="0" t="s">
         <v>705</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>702</v>
       </c>
       <c r="D8" s="16" t="n">
         <f aca="false">u_hp_26*g_hp_26</f>
@@ -42987,10 +44479,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D9" s="16" t="n">
         <f aca="false">u_amd_26*g_amd_26</f>
@@ -43007,10 +44499,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D10" s="16" t="n">
         <f aca="false">u_tpu_26*g_tpu_26</f>
@@ -43027,10 +44519,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D11" s="16" t="n">
         <f aca="false">u_trn_26*g_trn_26</f>
@@ -43047,10 +44539,10 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D12" s="16" t="n">
         <f aca="false">u_oth_26*g_oth_26</f>
@@ -43067,10 +44559,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">SUM(D5:D12)/1000</f>
@@ -43091,10 +44583,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D14" s="14" t="n">
         <f aca="false">D13*hbm_gross</f>
@@ -43115,7 +44607,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>421</v>
@@ -43133,12 +44625,12 @@
         <v>26.5</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>429</v>
@@ -43158,10 +44650,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">D17/(1+hbm_g26)</f>
@@ -43184,12 +44676,12 @@
         <v>11.477169466875</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>222</v>
@@ -43209,12 +44701,12 @@
         <v>1</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>222</v>
@@ -43234,12 +44726,12 @@
         <v>0.85</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>222</v>
@@ -43259,15 +44751,15 @@
         <v>0.6</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D21" s="14" t="n">
         <f aca="false">D14*D18</f>
@@ -43288,10 +44780,10 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D22" s="14" t="n">
         <f aca="false">D14*D19</f>
@@ -43312,10 +44804,10 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D23" s="14" t="n">
         <f aca="false">D14*D20</f>
@@ -43336,10 +44828,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C24" s="14" t="n">
         <f aca="false">C17</f>
@@ -43362,15 +44854,15 @@
         <v>11.477169466875</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C25" s="14" t="n">
         <f aca="false">C17</f>
@@ -43395,10 +44887,10 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C26" s="14" t="n">
         <f aca="false">C17</f>
@@ -43423,10 +44915,10 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D27" s="14" t="n">
         <f aca="false">D21-D17</f>
@@ -43447,10 +44939,10 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D28" s="14" t="n">
         <f aca="false">D22-D17</f>
@@ -43471,10 +44963,10 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="D29" s="14" t="n">
         <f aca="false">D23-D17</f>
@@ -43495,10 +44987,10 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C30" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -43523,10 +45015,10 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -43551,10 +45043,10 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C32" s="14" t="n">
         <f aca="false">hbm_mkt25/C24</f>
@@ -43579,10 +45071,10 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">C24*C30</f>
@@ -43607,10 +45099,10 @@
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">C25*C31</f>
@@ -43635,10 +45127,10 @@
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C35" s="17" t="n">
         <f aca="false">C26*C32</f>
@@ -43663,15 +45155,15 @@
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D38" s="17" t="n">
         <f aca="false">(D5+D6+D7+D8)/1000*hbm_p26</f>
@@ -43680,22 +45172,22 @@
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D39" s="17" t="n">
         <f aca="false">nv_dc26*nv_hbm/nv_content</f>
         <v>38.9728971962617</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="B40" s="0" t="s">
         <v>48</v>
@@ -43707,7 +45199,7 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>421</v>
@@ -43721,15 +45213,15 @@
         <v>7.6</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D42" s="17" t="n">
         <f aca="false">pub26_lo</f>
@@ -43746,7 +45238,7 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="B43" s="0" t="s">
         <v>48</v>
@@ -43785,7 +45277,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43793,36 +45285,36 @@
         <v>27</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B4" s="18" t="n">
         <v>19.1</v>
@@ -43857,7 +45349,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="F5" s="14" t="n">
         <f aca="false">F4*0.68</f>
@@ -43882,7 +45374,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="F6" s="14" t="n">
         <f aca="false">F4*0.32</f>
@@ -43907,7 +45399,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="F7" s="0" t="n">
         <f aca="false">F4-F5-F6</f>
@@ -43932,7 +45424,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="F8" s="14" t="n">
         <f aca="false">F4*(1-0.745-0.07)</f>
@@ -43957,7 +45449,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="F9" s="0" t="n">
         <f aca="false">F4-F8-F10</f>
@@ -43982,7 +45474,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>3.1</v>
@@ -44017,7 +45509,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="B11" s="19" t="n">
         <f aca="false">IF(B4=0,"",B10/B4)</f>
@@ -44058,7 +45550,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>8</v>
@@ -44093,7 +45585,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B13" s="18" t="n">
         <v>5</v>
@@ -44128,7 +45620,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="G14" s="0" t="n">
         <v>1</v>
@@ -44144,7 +45636,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="G15" s="0" t="n">
         <v>1</v>
@@ -44160,7 +45652,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
   </sheetData>
@@ -44189,12 +45681,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44202,72 +45694,72 @@
         <v>27</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="O3" s="13" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="P3" s="13" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="Q3" s="13" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="S3" s="13" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="T3" s="13" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="U3" s="13" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">SUM(Q!B4:E4)</f>
@@ -44316,7 +45808,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C5" s="17" t="n">
         <f aca="false">Q!J5-C6</f>
@@ -44359,12 +45851,12 @@
         <v>158.582541988058</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="C6" s="17" t="n">
         <f aca="false">(Mkt!D33/4*sh26+Mkt!D33/4*sh26+Mkt!D33/4*sh26+Mkt!D33/4*sh26)*fx/1000</f>
@@ -44407,12 +45899,12 @@
         <v>75.3957801559872</v>
       </c>
       <c r="V6" s="8" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">Q!J6</f>
@@ -44457,7 +45949,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">Q!J7</f>
@@ -44502,7 +45994,7 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C9" s="19" t="n">
         <f aca="false">C6/C4</f>
@@ -44547,7 +46039,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">SUM(Q!B13:E13)</f>
@@ -44596,7 +46088,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">w_c*(1+cb_1)+w_h*D31/C31+w_n*(1+nb_1)</f>
@@ -44637,7 +46129,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C12" s="17" t="n">
         <f aca="false">Q!J8</f>
@@ -44680,12 +46172,12 @@
         <v>110.782148943506</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">Q!J9</f>
@@ -44730,7 +46222,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B14" s="17" t="n">
         <f aca="false">SUM(Q!B10:E10)</f>
@@ -44779,7 +46271,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">B14/B4</f>
@@ -44828,7 +46320,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">nm_rev_0</f>
@@ -44873,7 +46365,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">nm_op_0</f>
@@ -44918,7 +46410,7 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">C4+C16</f>
@@ -44997,12 +46489,12 @@
         <v>557.69874365526</v>
       </c>
       <c r="V18" s="8" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C19" s="17" t="n">
         <f aca="false">C14+C17</f>
@@ -45047,7 +46539,7 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B20" s="17" t="n">
         <f aca="false">SUM(Q!B12:E12)</f>
@@ -45130,12 +46622,12 @@
         <v>57.927163053201</v>
       </c>
       <c r="V20" s="4" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">cap_0</f>
@@ -45180,7 +46672,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">C20+C10-C21</f>
@@ -45225,7 +46717,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">div_0</f>
@@ -45270,7 +46762,7 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">bb_0</f>
@@ -45313,12 +46805,12 @@
         <v>61.2301176183749</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">eq_last+(Q!H12+Q!I12)+extra_eq-C24-C23</f>
@@ -45363,7 +46855,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="C26" s="17" t="n">
         <f aca="false">nc_last+(Q!H12+Q!I12)+(Q!H13+Q!I13)-capex_rem+extra_eq-C24-C23</f>
@@ -45408,7 +46900,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C27" s="17" t="n">
         <f aca="false">sh_last+extra_sh-bb_sh_0</f>
@@ -45489,7 +46981,7 @@
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C28" s="21" t="n">
         <f aca="false">C25/C27*1000000</f>
@@ -45534,7 +47026,7 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="C29" s="21" t="n">
         <f aca="false">C20/C27*1000000</f>
@@ -45615,7 +47107,7 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C30" s="15" t="n">
         <f aca="false">C20/C25</f>
@@ -45660,7 +47152,7 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">(Mkt!D24/4*sh26+Mkt!D24/4*sh26+Mkt!D24/4*sh26+Mkt!D24/4*sh26)</f>
@@ -45705,7 +47197,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="D32" s="19" t="n">
         <f aca="false">D18/C18-1</f>
@@ -45782,7 +47274,7 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C33" s="19" t="n">
         <f aca="false">C20/C18</f>
@@ -45891,30 +47383,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45926,10 +47418,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="E4" s="21" t="n">
         <f aca="false">Y!C28</f>
@@ -45946,17 +47438,17 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B5" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="E5" s="21" t="n">
         <f aca="false">Y!C28</f>
@@ -45973,17 +47465,17 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B6" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="E6" s="21" t="n">
         <f aca="false">Y!C28</f>
@@ -46007,10 +47499,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E7" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -46027,17 +47519,17 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E8" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -46054,17 +47546,17 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E9" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -46088,10 +47580,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E10" s="21" t="n">
         <f aca="false">Y!G28</f>
@@ -46108,17 +47600,17 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E11" s="21" t="n">
         <f aca="false">Y!G28</f>
@@ -46135,17 +47627,17 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E12" s="21" t="n">
         <f aca="false">Y!G28</f>
@@ -46169,10 +47661,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E13" s="21" t="n">
         <f aca="false">Y!J28</f>
@@ -46189,17 +47681,17 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B14" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E14" s="21" t="n">
         <f aca="false">Y!J28</f>
@@ -46216,17 +47708,17 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B15" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E15" s="21" t="n">
         <f aca="false">Y!J28</f>
@@ -46250,10 +47742,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E16" s="21" t="n">
         <f aca="false">Y!E28</f>
@@ -46270,17 +47762,17 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E17" s="21" t="n">
         <f aca="false">Y!E28</f>
@@ -46297,17 +47789,17 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E18" s="21" t="n">
         <f aca="false">Y!E28</f>
@@ -46331,10 +47823,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E19" s="21" t="n">
         <f aca="false">Y!H28</f>
@@ -46351,17 +47843,17 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B20" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E20" s="21" t="n">
         <f aca="false">Y!H28</f>
@@ -46378,17 +47870,17 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B21" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E21" s="21" t="n">
         <f aca="false">Y!H28</f>
@@ -46412,10 +47904,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E22" s="21" t="n">
         <f aca="false">Y!K28</f>
@@ -46432,17 +47924,17 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B23" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E23" s="21" t="n">
         <f aca="false">Y!K28</f>
@@ -46459,17 +47951,17 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B24" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E24" s="21" t="n">
         <f aca="false">Y!K28</f>
@@ -46493,10 +47985,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E25" s="21" t="n">
         <f aca="false">Y!F28</f>
@@ -46513,17 +48005,17 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B26" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E26" s="21" t="n">
         <f aca="false">Y!F28</f>
@@ -46540,17 +48032,17 @@
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B27" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E27" s="21" t="n">
         <f aca="false">Y!F28</f>
@@ -46574,10 +48066,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E28" s="21" t="n">
         <f aca="false">Y!I28</f>
@@ -46594,17 +48086,17 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B29" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E29" s="21" t="n">
         <f aca="false">Y!I28</f>
@@ -46621,17 +48113,17 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B30" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E30" s="21" t="n">
         <f aca="false">Y!I28</f>
@@ -46655,10 +48147,10 @@
         <v>1</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E31" s="21" t="n">
         <f aca="false">Y!L28</f>
@@ -46675,17 +48167,17 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B32" s="0" t="n">
         <f aca="false">pb_2</f>
         <v>1.4</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E32" s="21" t="n">
         <f aca="false">Y!L28</f>
@@ -46702,17 +48194,17 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">pb_3</f>
         <v>2</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E33" s="21" t="n">
         <f aca="false">Y!L28</f>
@@ -46736,10 +48228,10 @@
         <v>4</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E34" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -46763,10 +48255,10 @@
         <v>8</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E35" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -46790,10 +48282,10 @@
         <v>12</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E36" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -46817,10 +48309,10 @@
         <v>4</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E37" s="21" t="n">
         <f aca="false">Y!G29</f>
@@ -46844,10 +48336,10 @@
         <v>8</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E38" s="21" t="n">
         <f aca="false">Y!G29</f>
@@ -46871,10 +48363,10 @@
         <v>12</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E39" s="21" t="n">
         <f aca="false">Y!G29</f>
@@ -46898,10 +48390,10 @@
         <v>4</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E40" s="21" t="n">
         <f aca="false">Y!J29</f>
@@ -46925,10 +48417,10 @@
         <v>8</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E41" s="21" t="n">
         <f aca="false">Y!J29</f>
@@ -46952,10 +48444,10 @@
         <v>12</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E42" s="21" t="n">
         <f aca="false">Y!J29</f>
@@ -46979,10 +48471,10 @@
         <v>4</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E43" s="21" t="n">
         <f aca="false">Y!E29</f>
@@ -47006,10 +48498,10 @@
         <v>8</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E44" s="21" t="n">
         <f aca="false">Y!E29</f>
@@ -47033,10 +48525,10 @@
         <v>12</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E45" s="21" t="n">
         <f aca="false">Y!E29</f>
@@ -47060,10 +48552,10 @@
         <v>4</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E46" s="21" t="n">
         <f aca="false">Y!H29</f>
@@ -47087,10 +48579,10 @@
         <v>8</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E47" s="21" t="n">
         <f aca="false">Y!H29</f>
@@ -47114,10 +48606,10 @@
         <v>12</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E48" s="21" t="n">
         <f aca="false">Y!H29</f>
@@ -47141,10 +48633,10 @@
         <v>4</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E49" s="21" t="n">
         <f aca="false">Y!K29</f>
@@ -47168,10 +48660,10 @@
         <v>8</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E50" s="21" t="n">
         <f aca="false">Y!K29</f>
@@ -47195,10 +48687,10 @@
         <v>12</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E51" s="21" t="n">
         <f aca="false">Y!K29</f>
@@ -47222,10 +48714,10 @@
         <v>4</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E52" s="21" t="n">
         <f aca="false">Y!F29</f>
@@ -47249,10 +48741,10 @@
         <v>8</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E53" s="21" t="n">
         <f aca="false">Y!F29</f>
@@ -47276,10 +48768,10 @@
         <v>12</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E54" s="21" t="n">
         <f aca="false">Y!F29</f>
@@ -47303,10 +48795,10 @@
         <v>4</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E55" s="21" t="n">
         <f aca="false">Y!I29</f>
@@ -47330,10 +48822,10 @@
         <v>8</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E56" s="21" t="n">
         <f aca="false">Y!I29</f>
@@ -47357,10 +48849,10 @@
         <v>12</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E57" s="21" t="n">
         <f aca="false">Y!I29</f>
@@ -47384,10 +48876,10 @@
         <v>4</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E58" s="21" t="n">
         <f aca="false">Y!L29</f>
@@ -47411,10 +48903,10 @@
         <v>8</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E59" s="21" t="n">
         <f aca="false">Y!L29</f>
@@ -47438,10 +48930,10 @@
         <v>12</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E60" s="21" t="n">
         <f aca="false">Y!L29</f>
@@ -47458,55 +48950,55 @@
     </row>
     <row r="63" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B68" s="18" t="n">
         <v>1.27</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="B69" s="18" t="n">
         <v>1.59</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="B70" s="18" t="n">
         <v>1.04</v>
@@ -47514,7 +49006,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="B71" s="18" t="n">
         <v>1.41</v>
@@ -47522,7 +49014,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B72" s="18" t="n">
         <v>1.97</v>
@@ -47530,7 +49022,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="B73" s="18" t="n">
         <v>1.73</v>
@@ -47538,7 +49030,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="B74" s="18" t="n">
         <v>1.04</v>
@@ -47546,7 +49038,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="B75" s="18" t="n">
         <v>1.43</v>
@@ -47554,7 +49046,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="B76" s="18" t="n">
         <v>0.8865</v>
@@ -47562,7 +49054,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="B77" s="18" t="n">
         <v>1.96</v>
@@ -47570,7 +49062,7 @@
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="B78" s="14" t="n">
         <f aca="false">PERCENTILE(B68:B77,0.25)</f>
@@ -47579,7 +49071,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="B79" s="14" t="n">
         <f aca="false">MEDIAN(B68:B77)</f>
@@ -47588,7 +49080,7 @@
     </row>
     <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="B80" s="14" t="n">
         <f aca="false">PERCENTILE(B68:B77,0.75)</f>
@@ -47597,7 +49089,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B81" s="14" t="n">
         <f aca="false">MIN(B68:B77)</f>
@@ -47606,7 +49098,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B82" s="14" t="n">
         <f aca="false">MAX(B68:B77)</f>
@@ -47615,7 +49107,7 @@
     </row>
     <row r="83" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="B83" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B78),2)</f>
@@ -47624,7 +49116,7 @@
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B84" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B79),2)</f>
@@ -47633,7 +49125,7 @@
     </row>
     <row r="85" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B85" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B80),2)</f>
@@ -47642,7 +49134,7 @@
     </row>
     <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="B86" s="14" t="n">
         <f aca="false">ROUND(MIN(B81),2)</f>
@@ -47651,7 +49143,7 @@
     </row>
     <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="B87" s="14" t="n">
         <f aca="false">ROUND(MAX(B82),2)</f>
@@ -47660,48 +49152,48 @@
     </row>
     <row r="89" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="C91" s="14" t="n">
         <f aca="false">B83</f>
         <v>1.1</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="E91" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -47722,17 +49214,17 @@
     </row>
     <row r="92" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="C92" s="14" t="n">
         <f aca="false">B84</f>
         <v>1.42</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="E92" s="21" t="n">
         <f aca="false">Y!D28</f>
@@ -47753,17 +49245,17 @@
     </row>
     <row r="93" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="C93" s="14" t="n">
         <f aca="false">B85</f>
         <v>1.7</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="E93" s="21" t="n">
         <f aca="false">Y!K28</f>
@@ -47784,48 +49276,48 @@
     </row>
     <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B98" s="18" t="n">
         <v>9.15</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="B99" s="18" t="n">
         <v>6.95</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="B100" s="18" t="n">
         <v>5.06</v>
@@ -47833,7 +49325,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="B101" s="18" t="n">
         <v>15.3</v>
@@ -47841,7 +49333,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="B102" s="18" t="n">
         <v>19.1</v>
@@ -47849,7 +49341,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="B103" s="18" t="n">
         <v>12.5</v>
@@ -47860,7 +49352,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="B104" s="18" t="n">
         <v>6.5</v>
@@ -47871,7 +49363,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="B105" s="18" t="n">
         <v>36.1</v>
@@ -47882,7 +49374,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="B106" s="18" t="n">
         <v>10.6</v>
@@ -47893,7 +49385,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="B107" s="18" t="n">
         <v>18.2</v>
@@ -47904,7 +49396,7 @@
     </row>
     <row r="108" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="B108" s="14" t="n">
         <f aca="false">PERCENTILE(B98:B107,0.25)</f>
@@ -47917,7 +49409,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="B109" s="14" t="n">
         <f aca="false">MEDIAN(B98:B107)</f>
@@ -47930,7 +49422,7 @@
     </row>
     <row r="110" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="B110" s="14" t="n">
         <f aca="false">PERCENTILE(B98:B107,0.75)</f>
@@ -47943,7 +49435,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B111" s="14" t="n">
         <f aca="false">MIN(B98:B107)</f>
@@ -47956,7 +49448,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B112" s="14" t="n">
         <f aca="false">MAX(B98:B107)</f>
@@ -47969,7 +49461,7 @@
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="B113" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B108),2)</f>
@@ -47978,7 +49470,7 @@
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="B114" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B109),2)</f>
@@ -47987,7 +49479,7 @@
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="B115" s="14" t="n">
         <f aca="false">ROUND(AVERAGE(B110),2)</f>
@@ -47996,7 +49488,7 @@
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="B116" s="14" t="n">
         <f aca="false">ROUND(MIN(B111),2)</f>
@@ -48005,7 +49497,7 @@
     </row>
     <row r="117" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="B117" s="14" t="n">
         <f aca="false">ROUND(MAX(B112),2)</f>
@@ -48014,48 +49506,48 @@
     </row>
     <row r="119" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="6" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="5" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="4" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="C121" s="14" t="n">
         <f aca="false">B113</f>
         <v>7.5</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="E121" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -48076,17 +49568,17 @@
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="4" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="C122" s="14" t="n">
         <f aca="false">B114</f>
         <v>11.55</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="E122" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -48107,17 +49599,17 @@
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="4" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="C123" s="14" t="n">
         <f aca="false">B115</f>
         <v>17.48</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="E123" s="21" t="n">
         <f aca="false">Y!K29</f>
@@ -48138,12 +49630,12 @@
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="6" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48151,29 +49643,29 @@
         <v>27</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="4" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="B130" s="21" t="n">
         <f aca="false">Y!D29</f>
@@ -48190,7 +49682,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B131" s="21" t="n">
         <f aca="false">Y!E29</f>
@@ -48207,7 +49699,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="B132" s="21" t="n">
         <f aca="false">Y!F29</f>
@@ -48224,7 +49716,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B133" s="21" t="n">
         <f aca="false">Y!M29</f>
@@ -48241,7 +49733,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B134" s="21" t="n">
         <f aca="false">Y!N29</f>
@@ -48258,7 +49750,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B135" s="21" t="n">
         <f aca="false">Y!O29</f>
@@ -48275,27 +49767,27 @@
     </row>
     <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="4" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="4" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="B137" s="19" t="n">
         <f aca="false">MIN(tp_g/tp_roe,0.8)</f>
         <v>0.49813200498132</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="B138" s="21" t="n">
         <f aca="false">Y!D22/Y!D27*1000000</f>
@@ -48312,7 +49804,7 @@
     </row>
     <row r="139" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="B139" s="21" t="n">
         <f aca="false">Y!E22/Y!E27*1000000</f>
@@ -48329,7 +49821,7 @@
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B140" s="21" t="n">
         <f aca="false">Y!F22/Y!F27*1000000</f>
@@ -48346,7 +49838,7 @@
     </row>
     <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B141" s="21" t="n">
         <f aca="false">B133*(1-$B$137)</f>
@@ -48363,7 +49855,7 @@
     </row>
     <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B142" s="21" t="n">
         <f aca="false">B134*(1-$B$137)</f>
@@ -48380,7 +49872,7 @@
     </row>
     <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="B143" s="21" t="n">
         <f aca="false">B135*(1-$B$137)</f>
@@ -48397,7 +49889,7 @@
     </row>
     <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="B144" s="21" t="n">
         <f aca="false">SUMPRODUCT(B138:B143,1/(1+tp_r)^{1;2;3;4;5;6})+B143*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6</f>
@@ -48412,12 +49904,12 @@
         <v>198984.090272765</v>
       </c>
       <c r="E144" s="8" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="B145" s="21" t="n">
         <f aca="false">B144*(1+tp_r)</f>
@@ -48434,36 +49926,36 @@
     </row>
     <row r="146" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B146" s="25" t="n">
         <f aca="false">tp_wA*B145+tp_wB*C145+tp_wC*D145</f>
         <v>486542.246351878</v>
       </c>
       <c r="E146" s="8" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="6" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="5" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>32</v>
@@ -48471,19 +49963,19 @@
     </row>
     <row r="150" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="B150" s="0" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C150" s="18" t="n">
         <v>1.35</v>
       </c>
       <c r="D150" s="8" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="E150" s="8" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>65</v>
@@ -48491,19 +49983,19 @@
     </row>
     <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="4" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="B151" s="0" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="C151" s="18" t="n">
         <v>3.35</v>
       </c>
       <c r="D151" s="8" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="E151" s="8" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="F151" s="8" t="s">
         <v>65</v>
@@ -48511,19 +50003,19 @@
     </row>
     <row r="152" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="4" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B152" s="0" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="C152" s="18" t="n">
         <v>2.22</v>
       </c>
       <c r="D152" s="8" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="E152" s="8" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="F152" s="8" t="s">
         <v>65</v>
@@ -48531,19 +50023,19 @@
     </row>
     <row r="153" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="4" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="B153" s="0" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="C153" s="18" t="n">
         <v>1.66</v>
       </c>
       <c r="D153" s="8" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="E153" s="8" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="F153" s="8" t="s">
         <v>65</v>
@@ -48551,55 +50043,55 @@
     </row>
     <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="4" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B154" s="14" t="n">
         <f aca="false">MEDIAN(C150:C153)</f>
         <v>1.94</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="B155" s="21" t="n">
         <f aca="false">tp_wA*Y!E28+tp_wB*Y!H28+tp_wC*Y!K28</f>
         <v>241105.206895339</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B156" s="25" t="n">
         <f aca="false">B154*B155</f>
         <v>467744.101376957</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="4" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="B157" s="21" t="n">
         <f aca="false">tp_wA*(2/12*Y!D29+10/12*Y!E29)+tp_wB*(2/12*Y!G29+10/12*Y!H29)+tp_wC*(2/12*Y!J29+10/12*Y!K29)</f>
         <v>78917.4698331062</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="6" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48607,29 +50099,29 @@
         <v>27</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="C160" s="5"/>
       <c r="D160" s="5"/>
       <c r="E160" s="5" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="4" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="B161" s="25" t="n">
         <f aca="false">tp_w_dcf*B146+(1-tp_w_dcf)*B156</f>
         <v>477143.173864418</v>
       </c>
       <c r="E161" s="8" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B162" s="21" t="n">
         <f aca="false">B156</f>
@@ -48638,31 +50130,31 @@
     </row>
     <row r="163" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="4" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="B163" s="21" t="n">
         <f aca="false">cons_tp</f>
         <v>478906</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="4" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="B164" s="19" t="n">
         <f aca="false">B161/px-1</f>
         <v>1.21412145644741</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="4" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="B165" s="19" t="n">
         <f aca="false">B162/px-1</f>
@@ -48671,7 +50163,7 @@
     </row>
     <row r="166" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="0" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B166" s="26" t="n">
         <f aca="false">B145/px</f>
@@ -48686,36 +50178,36 @@
         <v>1.01569605243639</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="4" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B167" s="19" t="n">
         <f aca="false">B155/cons_bvps28-1</f>
         <v>0.0390002667270208</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="4" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B168" s="19" t="n">
         <f aca="false">B157/(2/12*cons_eps27+10/12*cons_eps28)-1</f>
         <v>0.0523872812426651</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="4" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="B169" s="19" t="n">
         <f aca="false">(cons_tp/cons_bvps28)/B154-1</f>
@@ -48728,19 +50220,19 @@
     </row>
     <row r="170" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="4" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="B170" s="27" t="str">
         <f aca="false">TEXT(D145,"#,##0")&amp;"～"&amp;TEXT(B145,"#,##0")</f>
         <v>218,882～818,535</v>
       </c>
       <c r="E170" s="8" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="4" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="B171" s="15" t="n">
         <f aca="false">IF(px/Y!E28&gt;=MAX($B$68:$B$77),1,IF(px/Y!E28&lt;=MIN($B$68:$B$77),0,PERCENTRANK($B$68:$B$77,px/Y!E28)))</f>
@@ -48755,12 +50247,12 @@
         <v>0.111</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="4" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="B172" s="0" t="str">
         <f aca="false">"DCF：股東現金流 2027–2029 用每股（淨利＋折舊－資本支出；折舊與資本支出為記憶體事業口徑，淨利為合併），2030–2032 收斂期用 EPS ×（1 − g／ROE），r 10%、g 4%、ROE 為 2023–2025 平均約 8%（再投資率約五成）；明確期＋永續，基準日 2026 年底。Comparable：SK 海力士、美光、鎧俠、南亞科前瞻 P/B 中位數 × 2028 年底每"&amp;"股淨值（情境加權）。收斂期（2030–2032）淨利率收斂到循環中段：A 十年平均 × 1.2、B 十年平均、C 十年平均 × 0.8（In 頁 cyc_mA／cyc_mC），永續期以 2032 中段水準為基礎。偏誤：2027–2029 仍為高峰期盈餘且權重大，DCF 仍可能偏高估；純記憶體同業倍數未含集團折價，Comparable 偏高估。情境對應：A＝順利、B＝平平、C＝不如預期（原為 Tre"&amp;"ndForce／BofA 型價格情境）。"&amp;IF(MAX(B166:D166)&gt;3,"注意：DCF ÷ 現價有情境高於 3 倍（見上方「DCF ÷ 現價」列）；DCF 對收斂期淨利率與永續假設敏感，宜與 Comparable、市場共識並讀。","")</f>
@@ -48769,7 +50261,7 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48777,29 +50269,29 @@
         <v>27</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="C175" s="5"/>
       <c r="D175" s="5"/>
       <c r="E175" s="5" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="4" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="B176" s="21" t="n">
         <f aca="false">tp_wA*B178+tp_wB*B179+tp_wC*B180</f>
         <v>255831.994790815</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="4" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="B177" s="19" t="n">
         <f aca="false">B176/px-1</f>
@@ -48808,7 +50300,7 @@
     </row>
     <row r="178" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="4" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="B178" s="21" t="n">
         <f aca="false">B85*Y!D28</f>
@@ -48821,7 +50313,7 @@
     </row>
     <row r="179" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="4" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="B179" s="21" t="n">
         <f aca="false">B84*Y!G28</f>
@@ -48834,7 +50326,7 @@
     </row>
     <row r="180" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="4" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="B180" s="21" t="n">
         <f aca="false">B83*Y!J28</f>
@@ -48847,7 +50339,7 @@
     </row>
     <row r="181" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="4" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B181" s="15" t="n">
         <f aca="false">tp_wA</f>
@@ -48868,34 +50360,34 @@
     </row>
     <row r="182" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="4" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="4" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="B184" s="27" t="str">
         <f aca="false">IF(B164&gt;0.5,"大於 50%",IF(B164&gt;0.25,"25%–50%",IF(B164&gt;=0,"0%–25%",IF(B164&gt;=-0.25,"0%～−25%",IF(B164&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
         <v>大於 50%</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="4" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="B185" s="27" t="str">
         <f aca="false">IF(B164&gt;0.5,"強力買進",IF(B164&gt;0.25,"買進",IF(B164&gt;=-0.25,"中立",IF(B164&gt;=-0.5,"放空","強力放空"))))</f>
         <v>強力買進</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
     </row>
   </sheetData>
@@ -48923,29 +50415,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>30</v>
@@ -48957,10 +50449,10 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="C5" s="17" t="n">
         <f aca="false">-0.2*Y!D5</f>
@@ -48977,10 +50469,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C6" s="17" t="n">
         <f aca="false">0.2*Y!D5</f>
@@ -48997,10 +50489,10 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">-0.3*Y!D6</f>
@@ -49017,10 +50509,10 @@
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">0.3*Y!D6</f>
@@ -49037,10 +50529,10 @@
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="C9" s="17" t="n">
         <f aca="false">-0.3*Y!D7</f>
@@ -49057,10 +50549,10 @@
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C10" s="17" t="n">
         <f aca="false">0.3*Y!D7</f>
@@ -49077,7 +50569,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>30</v>
@@ -49089,10 +50581,10 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">-0.2*Y!H5</f>
@@ -49109,10 +50601,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C14" s="17" t="n">
         <f aca="false">0.2*Y!H5</f>
@@ -49129,10 +50621,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C15" s="17" t="n">
         <f aca="false">-0.3*Y!H6</f>
@@ -49149,10 +50641,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">0.3*Y!H6</f>
@@ -49169,10 +50661,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">-0.3*Y!H7</f>
@@ -49189,10 +50681,10 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">0.3*Y!H7</f>
@@ -49209,7 +50701,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>30</v>
@@ -49221,10 +50713,10 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">-0.2*Y!K5</f>
@@ -49241,10 +50733,10 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">0.2*Y!K5</f>
@@ -49261,10 +50753,10 @@
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">-0.3*Y!K6</f>
@@ -49281,10 +50773,10 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">0.3*Y!K6</f>
@@ -49301,10 +50793,10 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">-0.3*Y!K7</f>
@@ -49321,10 +50813,10 @@
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C26" s="17" t="n">
         <f aca="false">0.3*Y!K7</f>
@@ -49341,7 +50833,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>30</v>
@@ -49353,10 +50845,10 @@
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="C29" s="17" t="n">
         <f aca="false">-0.2*Y!L5</f>
@@ -49373,10 +50865,10 @@
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="C30" s="17" t="n">
         <f aca="false">0.2*Y!L5</f>
@@ -49393,10 +50885,10 @@
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C31" s="17" t="n">
         <f aca="false">-0.3*Y!L6</f>
@@ -49413,10 +50905,10 @@
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="C32" s="17" t="n">
         <f aca="false">0.3*Y!L6</f>
@@ -49433,10 +50925,10 @@
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">-0.3*Y!L7</f>
@@ -49453,10 +50945,10 @@
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">0.3*Y!L7</f>
@@ -49473,32 +50965,32 @@
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49506,7 +50998,7 @@
         <v>30</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="C40" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -49527,10 +51019,10 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="C41" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+(tp_r+0.01))^1+Val!B139/(1+(tp_r+0.01))^2+Val!B140/(1+(tp_r+0.01))^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*(Val!C138/(1+(tp_r+0.01))^1+Val!C139/(1+(tp_r+0.01))^2+Val!C140/(1+(tp_r+0.01))^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*(Val!D138/(1+(tp_r+0.01))^1+Val!D139/(1+(tp_r+0.01))^2+Val!D140/(1+(tp_r+0.01))^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
@@ -49551,10 +51043,10 @@
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="C42" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+(tp_r-0.01))^1+Val!B139/(1+(tp_r-0.01))^2+Val!B140/(1+(tp_r-0.01))^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*(Val!C138/(1+(tp_r-0.01))^1+Val!C139/(1+(tp_r-0.01))^2+Val!C140/(1+(tp_r-0.01))^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*(Val!D138/(1+(tp_r-0.01))^1+Val!D139/(1+(tp_r-0.01))^2+Val!D140/(1+(tp_r-0.01))^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
@@ -49575,10 +51067,10 @@
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="C43" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
@@ -49599,10 +51091,10 @@
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="C44" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
@@ -49623,10 +51115,10 @@
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="C45" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -49647,10 +51139,10 @@
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="C46" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
@@ -49671,7 +51163,7 @@
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="C47" s="28" t="n">
         <f aca="false">C40-Val!B146</f>
@@ -49703,7 +51195,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49711,21 +51203,21 @@
         <v>27</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">Q!H10+nm_op_q</f>
@@ -49739,12 +51231,12 @@
         <v>0.0383651864059591</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">Y!C18</f>
@@ -49758,12 +51250,12 @@
         <v>0.0221156435576788</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">Y!C19</f>
@@ -49777,12 +51269,12 @@
         <v>0.0516479449262781</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">Y!C20</f>
@@ -49796,12 +51288,12 @@
         <v>0.0479415417578637</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="B8" s="17" t="n">
         <f aca="false">Y!D19</f>
@@ -49815,12 +51307,12 @@
         <v>0.159533803455726</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">Y!D20</f>
@@ -49834,12 +51326,12 @@
         <v>0.176122795889556</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">Y!E19</f>
@@ -49853,12 +51345,12 @@
         <v>0.247012110688031</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">Y!D29</f>
@@ -49873,12 +51365,12 @@
         <v>0.32575543502237</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">Y!E29</f>
@@ -49893,12 +51385,12 @@
         <v>0.720912929388087</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="B13" s="17" t="n">
         <f aca="false">Y!E28</f>
@@ -49913,7 +51405,7 @@
         <v>0.241532090173527</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>
